--- a/docs/downloads/20260828_Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20260828_Johor_Teduh_Weekly_Update.xlsx
@@ -947,7 +947,7 @@
         <v/>
       </c>
       <c r="AJ6" s="13" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AK6" s="14">
         <f>AJ6/$D$6</f>
@@ -955,7 +955,7 @@
       </c>
       <c r="AL6" s="10" t="inlineStr">
         <is>
-          <t>Latest sales - Block A: 190 units, Block B: 114 units</t>
+          <t>Latest sales - Block A: 191 units, Block B: 116 units</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
         <v/>
       </c>
       <c r="AJ7" s="13" t="n">
-        <v>962</v>
+        <v>972</v>
       </c>
       <c r="AK7" s="14">
         <f>AJ7/$D$7</f>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AL7" s="10" t="inlineStr">
         <is>
-          <t>Latest sales - Block A: 394 units, Block B: 373 units, Block C: 87 units, Block D: 108 units</t>
+          <t>Latest sales - Block A: 400 units, Block B: 376 units, Block C: 87 units, Block D: 109 units</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
         <v/>
       </c>
       <c r="AJ8" s="13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK8" s="14">
         <f>AJ8/$D$8</f>
@@ -1696,7 +1696,7 @@
         <v/>
       </c>
       <c r="AJ12" s="13" t="n">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="AK12" s="14">
         <f>AJ12/$D$12</f>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="AL12" s="10" t="inlineStr">
         <is>
-          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 493 units, Block B: 530 units, Block D: 473 units</t>
+          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 493 units, Block B: 531 units, Block D: 473 units</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
         <v/>
       </c>
       <c r="AJ14" s="13" t="n">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="AK14" s="14">
         <f>AJ14/$D$14</f>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="AL14" s="10" t="inlineStr">
         <is>
-          <t>Latest sales - Block A: 497 units, Block B: 255 units</t>
+          <t>Latest sales - Block A: 499 units, Block B: 257 units</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
         <v/>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AK18" s="14">
         <f>AJ18/$D$18</f>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="AL18" s="10" t="inlineStr">
         <is>
-          <t>Latest sales - Block A: 438 units, Block B: 286 units</t>
+          <t>Latest sales - Block A: 439 units, Block B: 286 units</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
         <v/>
       </c>
       <c r="AJ20" s="13" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AK20" s="14">
         <f>AJ20/$D$20</f>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="AL20" s="10" t="inlineStr">
         <is>
-          <t>Latest sales - Block A: 213 units, Block B: 89 units</t>
+          <t>Latest sales - Block A: 215 units, Block B: 91 units</t>
         </is>
       </c>
     </row>
